--- a/data/yard-inventory.xlsx
+++ b/data/yard-inventory.xlsx
@@ -33,10 +33,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="3">
+  <numFmts count="1">
     <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-    <numFmt numFmtId="200" formatCode="yyyy-mm-dd"/>
-    <numFmt numFmtId="201" formatCode="0"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -400,7 +398,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T22"/>
+  <dimension ref="A1:AA22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -463,6 +461,27 @@
       <c r="T1" t="str">
         <v>Last Updated</v>
       </c>
+      <c r="U1" t="str">
+        <v>Hours</v>
+      </c>
+      <c r="V1" t="str">
+        <v>Tire Type</v>
+      </c>
+      <c r="W1" t="str">
+        <v>Fuel Type</v>
+      </c>
+      <c r="X1" t="str">
+        <v>Mast Raised</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>Mast Lowered</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>Attachment</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>Capacity</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
@@ -525,6 +544,27 @@
       <c r="T2" t="str">
         <v>2026-06-09T18:47:21.253Z</v>
       </c>
+      <c r="U2">
+        <v>3426</v>
+      </c>
+      <c r="V2" t="str">
+        <v>Cushion</v>
+      </c>
+      <c r="W2" t="str">
+        <v>LP</v>
+      </c>
+      <c r="X2" t="str">
+        <v>217.5"FSV</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>SS FP</v>
+      </c>
+      <c r="AA2">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
@@ -587,6 +627,27 @@
       <c r="T3" t="str">
         <v>2026-06-09T18:47:21.254Z</v>
       </c>
+      <c r="U3">
+        <v>12961</v>
+      </c>
+      <c r="V3" t="str">
+        <v>Cushion</v>
+      </c>
+      <c r="W3" t="str">
+        <v>LP</v>
+      </c>
+      <c r="X3" t="str">
+        <v>80"FSV</v>
+      </c>
+      <c r="Y3" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z3" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AA3">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
@@ -649,6 +710,27 @@
       <c r="T4" t="str">
         <v>2026-06-09T18:47:21.254Z</v>
       </c>
+      <c r="U4">
+        <v>4039</v>
+      </c>
+      <c r="V4" t="str">
+        <v>Cushion</v>
+      </c>
+      <c r="W4" t="str">
+        <v>LP</v>
+      </c>
+      <c r="X4" t="str">
+        <v>189"FSV</v>
+      </c>
+      <c r="Y4" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z4" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AA4">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
@@ -711,6 +793,27 @@
       <c r="T5" t="str">
         <v>2026-06-09T18:47:21.254Z</v>
       </c>
+      <c r="U5">
+        <v>4054</v>
+      </c>
+      <c r="V5" t="str">
+        <v>Cushion</v>
+      </c>
+      <c r="W5" t="str">
+        <v>LP</v>
+      </c>
+      <c r="X5" t="str">
+        <v>189"FSV</v>
+      </c>
+      <c r="Y5" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z5" t="str">
+        <v>SS FP</v>
+      </c>
+      <c r="AA5">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
@@ -773,6 +876,27 @@
       <c r="T6" t="str">
         <v>2026-06-09T18:47:21.255Z</v>
       </c>
+      <c r="U6">
+        <v>3181</v>
+      </c>
+      <c r="V6" t="str">
+        <v>Cushion</v>
+      </c>
+      <c r="W6" t="str">
+        <v>LP</v>
+      </c>
+      <c r="X6" t="str">
+        <v>189"FSV</v>
+      </c>
+      <c r="Y6" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z6" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AA6">
+        <v>3</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
@@ -835,6 +959,27 @@
       <c r="T7" t="str">
         <v>2026-06-09T18:47:21.255Z</v>
       </c>
+      <c r="U7">
+        <v>4089</v>
+      </c>
+      <c r="V7" t="str">
+        <v>Cushion</v>
+      </c>
+      <c r="W7" t="str">
+        <v>LP</v>
+      </c>
+      <c r="X7" t="str">
+        <v>189"FSV</v>
+      </c>
+      <c r="Y7" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z7" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AA7">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
@@ -897,6 +1042,27 @@
       <c r="T8" t="str">
         <v>2026-06-09T18:47:21.255Z</v>
       </c>
+      <c r="U8">
+        <v>4551</v>
+      </c>
+      <c r="V8" t="str">
+        <v>Cushion</v>
+      </c>
+      <c r="W8" t="str">
+        <v>LP</v>
+      </c>
+      <c r="X8" t="str">
+        <v>189"FSV</v>
+      </c>
+      <c r="Y8" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z8" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AA8">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
@@ -959,6 +1125,27 @@
       <c r="T9" t="str">
         <v>2026-06-09T18:47:21.255Z</v>
       </c>
+      <c r="U9">
+        <v>4224</v>
+      </c>
+      <c r="V9" t="str">
+        <v>Cushion</v>
+      </c>
+      <c r="W9" t="str">
+        <v>LP</v>
+      </c>
+      <c r="X9" t="str">
+        <v>189"FSV</v>
+      </c>
+      <c r="Y9" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z9" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AA9">
+        <v>5</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
@@ -1021,6 +1208,27 @@
       <c r="T10" t="str">
         <v>2026-06-09T18:47:21.255Z</v>
       </c>
+      <c r="U10">
+        <v>4624</v>
+      </c>
+      <c r="V10" t="str">
+        <v>Cushion</v>
+      </c>
+      <c r="W10" t="str">
+        <v>LP</v>
+      </c>
+      <c r="X10" t="str">
+        <v>189"FSV</v>
+      </c>
+      <c r="Y10" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z10" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AA10">
+        <v>5</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
@@ -1083,6 +1291,27 @@
       <c r="T11" t="str">
         <v>2026-06-09T18:47:21.255Z</v>
       </c>
+      <c r="U11">
+        <v>3116</v>
+      </c>
+      <c r="V11" t="str">
+        <v>Cushion</v>
+      </c>
+      <c r="W11" t="str">
+        <v>LP</v>
+      </c>
+      <c r="X11" t="str">
+        <v>189"FSV</v>
+      </c>
+      <c r="Y11" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z11" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AA11">
+        <v>5</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
@@ -1145,6 +1374,27 @@
       <c r="T12" t="str">
         <v>2026-06-09T18:47:21.255Z</v>
       </c>
+      <c r="U12">
+        <v>5992</v>
+      </c>
+      <c r="V12" t="str">
+        <v>Cushion</v>
+      </c>
+      <c r="W12" t="str">
+        <v>LP</v>
+      </c>
+      <c r="X12" t="str">
+        <v>189"FSV</v>
+      </c>
+      <c r="Y12" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z12" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AA12">
+        <v>5</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
@@ -1172,7 +1422,7 @@
         <v>Showroom</v>
       </c>
       <c r="I13" t="str">
-        <v>Section 6</v>
+        <v>Section 2</v>
       </c>
       <c r="J13" t="str">
         <v>C</v>
@@ -1181,10 +1431,10 @@
         <v>18</v>
       </c>
       <c r="L13" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M13" t="str">
-        <v>Available</v>
+        <v>Rental Ready</v>
       </c>
       <c r="N13" t="str">
         <v>Ready</v>
@@ -1205,7 +1455,28 @@
         <v>2026-06-09T18:47:21.255Z</v>
       </c>
       <c r="T13" t="str">
-        <v>2026-06-09T21:42:39.580Z</v>
+        <v>2026-06-10T15:58:49.455Z</v>
+      </c>
+      <c r="U13" t="str">
+        <v>6525</v>
+      </c>
+      <c r="V13" t="str">
+        <v>Cushion</v>
+      </c>
+      <c r="W13" t="str">
+        <v>LP</v>
+      </c>
+      <c r="X13" t="str">
+        <v>189"</v>
+      </c>
+      <c r="Y13" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z13" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AA13" t="str">
+        <v>5</v>
       </c>
     </row>
     <row r="14">
@@ -1269,6 +1540,27 @@
       <c r="T14" t="str">
         <v>2026-06-09T18:47:21.255Z</v>
       </c>
+      <c r="U14">
+        <v>5522</v>
+      </c>
+      <c r="V14" t="str">
+        <v>Pneumatic</v>
+      </c>
+      <c r="W14" t="str">
+        <v>LP</v>
+      </c>
+      <c r="X14" t="str">
+        <v>189"</v>
+      </c>
+      <c r="Y14" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z14" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AA14">
+        <v>5</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
@@ -1331,6 +1623,27 @@
       <c r="T15" t="str">
         <v>2026-06-09T18:47:21.256Z</v>
       </c>
+      <c r="U15">
+        <v>9926</v>
+      </c>
+      <c r="V15" t="str">
+        <v>Pneumatic</v>
+      </c>
+      <c r="W15" t="str">
+        <v>LP</v>
+      </c>
+      <c r="X15" t="str">
+        <v>189"</v>
+      </c>
+      <c r="Y15" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z15" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AA15">
+        <v>5</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
@@ -1393,6 +1706,27 @@
       <c r="T16" t="str">
         <v>2026-06-09T18:47:21.256Z</v>
       </c>
+      <c r="U16">
+        <v>9925</v>
+      </c>
+      <c r="V16" t="str">
+        <v>Cushion</v>
+      </c>
+      <c r="W16" t="str">
+        <v>LP</v>
+      </c>
+      <c r="X16" t="str">
+        <v>189"FSV</v>
+      </c>
+      <c r="Y16" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z16" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AA16">
+        <v>12</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
@@ -1455,6 +1789,27 @@
       <c r="T17" t="str">
         <v>2026-06-09T18:47:21.256Z</v>
       </c>
+      <c r="U17">
+        <v>2005</v>
+      </c>
+      <c r="V17" t="str">
+        <v>Pneumatic</v>
+      </c>
+      <c r="W17" t="str">
+        <v>DSL</v>
+      </c>
+      <c r="X17" t="str">
+        <v>189"</v>
+      </c>
+      <c r="Y17" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z17" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AA17">
+        <v>12</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
@@ -1517,6 +1872,27 @@
       <c r="T18" t="str">
         <v>2026-06-09T18:47:21.256Z</v>
       </c>
+      <c r="U18">
+        <v>10178</v>
+      </c>
+      <c r="V18" t="str">
+        <v>Cushion</v>
+      </c>
+      <c r="W18" t="str">
+        <v>LP</v>
+      </c>
+      <c r="X18" t="str">
+        <v>189"FSV</v>
+      </c>
+      <c r="Y18" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z18" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AA18">
+        <v>12</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
@@ -1579,6 +1955,27 @@
       <c r="T19" t="str">
         <v>2026-06-09T18:47:21.256Z</v>
       </c>
+      <c r="U19">
+        <v>9660</v>
+      </c>
+      <c r="V19" t="str">
+        <v>Pneumatic</v>
+      </c>
+      <c r="W19" t="str">
+        <v>DSL</v>
+      </c>
+      <c r="X19" t="str">
+        <v>189"</v>
+      </c>
+      <c r="Y19" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z19" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AA19">
+        <v>12</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
@@ -1641,6 +2038,27 @@
       <c r="T20" t="str">
         <v>2026-06-09T18:47:21.256Z</v>
       </c>
+      <c r="U20">
+        <v>9112</v>
+      </c>
+      <c r="V20" t="str">
+        <v>Pneumatic</v>
+      </c>
+      <c r="W20" t="str">
+        <v>LP</v>
+      </c>
+      <c r="X20" t="str">
+        <v>189"FSV</v>
+      </c>
+      <c r="Y20" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z20" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AA20">
+        <v>36</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
@@ -1703,16 +2121,37 @@
       <c r="T21" t="str">
         <v>2026-06-09T18:47:21.256Z</v>
       </c>
+      <c r="U21">
+        <v>8379</v>
+      </c>
+      <c r="V21" t="str">
+        <v>Cushion</v>
+      </c>
+      <c r="W21" t="str">
+        <v>LP</v>
+      </c>
+      <c r="X21" t="str">
+        <v>132"FSV</v>
+      </c>
+      <c r="Y21" t="str">
+        <v>89"</v>
+      </c>
+      <c r="Z21" t="str">
+        <v>SS</v>
+      </c>
+      <c r="AA21">
+        <v>36</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
         <v>YARD-000021</v>
       </c>
       <c r="B22" t="str">
-        <v>9999</v>
+        <v>8888</v>
       </c>
       <c r="C22" t="str">
-        <v>12555</v>
+        <v>15155</v>
       </c>
       <c r="D22" t="str">
         <v>Forklift</v>
@@ -1721,25 +2160,25 @@
         <v>Toyota</v>
       </c>
       <c r="F22" t="str">
-        <v>8fgu25</v>
+        <v>8fgcu18</v>
       </c>
       <c r="G22" t="str">
-        <v>2020</v>
+        <v>2000</v>
       </c>
       <c r="H22" t="str">
-        <v>Showroom</v>
+        <v>Transportation Bay</v>
       </c>
       <c r="I22" t="str">
-        <v>Section 5</v>
+        <v>Inbound</v>
       </c>
       <c r="J22" t="str">
-        <v>B</v>
+        <v>C</v>
       </c>
       <c r="K22" t="str">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="L22" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M22" t="str">
         <v>Available</v>
@@ -1751,24 +2190,45 @@
         <v>No</v>
       </c>
       <c r="P22" t="str">
-        <v>2026-06-09</v>
+        <v>2026-06-10</v>
       </c>
       <c r="Q22" t="str">
-        <v>Ethan</v>
+        <v/>
       </c>
       <c r="R22" t="str">
         <v/>
       </c>
       <c r="S22" t="str">
-        <v>2026-06-09T21:59:02.590Z</v>
+        <v>2026-06-10T15:43:18.235Z</v>
       </c>
       <c r="T22" t="str">
-        <v>2026-06-10T03:30:08.644Z</v>
+        <v>2026-06-10T15:57:52.007Z</v>
+      </c>
+      <c r="U22" t="str">
+        <v>5555</v>
+      </c>
+      <c r="V22" t="str">
+        <v>cushion</v>
+      </c>
+      <c r="W22" t="str">
+        <v>LP</v>
+      </c>
+      <c r="X22" t="str">
+        <v>89</v>
+      </c>
+      <c r="Y22" t="str">
+        <v>189</v>
+      </c>
+      <c r="Z22" t="str">
+        <v>ss</v>
+      </c>
+      <c r="AA22" t="str">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:T22"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AA22"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data/yard-inventory.xlsx
+++ b/data/yard-inventory.xlsx
@@ -509,7 +509,7 @@
         <v>Showroom</v>
       </c>
       <c r="I2" t="str">
-        <v>Section 6</v>
+        <v>Section 2</v>
       </c>
       <c r="J2" t="str">
         <v>C</v>
@@ -518,7 +518,7 @@
         <v>1</v>
       </c>
       <c r="L2" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M2" t="str">
         <v>Available</v>
@@ -539,12 +539,12 @@
         <v/>
       </c>
       <c r="S2" t="str">
-        <v>2026-06-09T18:47:21.253Z</v>
+        <v>2026-06-10T16:24:01.106Z</v>
       </c>
       <c r="T2" t="str">
-        <v>2026-06-09T18:47:21.253Z</v>
-      </c>
-      <c r="U2">
+        <v>2026-06-10T16:24:01.106Z</v>
+      </c>
+      <c r="U2" t="str">
         <v>3426</v>
       </c>
       <c r="V2" t="str">
@@ -562,7 +562,7 @@
       <c r="Z2" t="str">
         <v>SS FP</v>
       </c>
-      <c r="AA2">
+      <c r="AA2" t="str">
         <v>3</v>
       </c>
     </row>
@@ -592,7 +592,7 @@
         <v>Showroom</v>
       </c>
       <c r="I3" t="str">
-        <v>Section 6</v>
+        <v>Section 2</v>
       </c>
       <c r="J3" t="str">
         <v>C</v>
@@ -601,7 +601,7 @@
         <v>2</v>
       </c>
       <c r="L3" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M3" t="str">
         <v>Available</v>
@@ -622,12 +622,12 @@
         <v/>
       </c>
       <c r="S3" t="str">
-        <v>2026-06-09T18:47:21.254Z</v>
+        <v>2026-06-10T16:24:01.108Z</v>
       </c>
       <c r="T3" t="str">
-        <v>2026-06-09T18:47:21.254Z</v>
-      </c>
-      <c r="U3">
+        <v>2026-06-10T16:24:01.108Z</v>
+      </c>
+      <c r="U3" t="str">
         <v>12961</v>
       </c>
       <c r="V3" t="str">
@@ -645,7 +645,7 @@
       <c r="Z3" t="str">
         <v>SS</v>
       </c>
-      <c r="AA3">
+      <c r="AA3" t="str">
         <v>3</v>
       </c>
     </row>
@@ -675,7 +675,7 @@
         <v>Showroom</v>
       </c>
       <c r="I4" t="str">
-        <v>Section 6</v>
+        <v>Section 2</v>
       </c>
       <c r="J4" t="str">
         <v>C</v>
@@ -684,7 +684,7 @@
         <v>5</v>
       </c>
       <c r="L4" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M4" t="str">
         <v>Available</v>
@@ -705,12 +705,12 @@
         <v/>
       </c>
       <c r="S4" t="str">
-        <v>2026-06-09T18:47:21.254Z</v>
+        <v>2026-06-10T16:24:01.108Z</v>
       </c>
       <c r="T4" t="str">
-        <v>2026-06-09T18:47:21.254Z</v>
-      </c>
-      <c r="U4">
+        <v>2026-06-10T16:24:01.108Z</v>
+      </c>
+      <c r="U4" t="str">
         <v>4039</v>
       </c>
       <c r="V4" t="str">
@@ -728,7 +728,7 @@
       <c r="Z4" t="str">
         <v>SS</v>
       </c>
-      <c r="AA4">
+      <c r="AA4" t="str">
         <v>3</v>
       </c>
     </row>
@@ -758,7 +758,7 @@
         <v>Showroom</v>
       </c>
       <c r="I5" t="str">
-        <v>Section 6</v>
+        <v>Section 2</v>
       </c>
       <c r="J5" t="str">
         <v>C</v>
@@ -767,7 +767,7 @@
         <v>6</v>
       </c>
       <c r="L5" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M5" t="str">
         <v>Available</v>
@@ -788,12 +788,12 @@
         <v/>
       </c>
       <c r="S5" t="str">
-        <v>2026-06-09T18:47:21.254Z</v>
+        <v>2026-06-10T16:24:01.108Z</v>
       </c>
       <c r="T5" t="str">
-        <v>2026-06-09T18:47:21.254Z</v>
-      </c>
-      <c r="U5">
+        <v>2026-06-10T16:24:01.108Z</v>
+      </c>
+      <c r="U5" t="str">
         <v>4054</v>
       </c>
       <c r="V5" t="str">
@@ -811,7 +811,7 @@
       <c r="Z5" t="str">
         <v>SS FP</v>
       </c>
-      <c r="AA5">
+      <c r="AA5" t="str">
         <v>3</v>
       </c>
     </row>
@@ -841,7 +841,7 @@
         <v>Showroom</v>
       </c>
       <c r="I6" t="str">
-        <v>Section 6</v>
+        <v>Section 2</v>
       </c>
       <c r="J6" t="str">
         <v>C</v>
@@ -850,7 +850,7 @@
         <v>7</v>
       </c>
       <c r="L6" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M6" t="str">
         <v>Available</v>
@@ -871,12 +871,12 @@
         <v/>
       </c>
       <c r="S6" t="str">
-        <v>2026-06-09T18:47:21.255Z</v>
+        <v>2026-06-10T16:24:01.109Z</v>
       </c>
       <c r="T6" t="str">
-        <v>2026-06-09T18:47:21.255Z</v>
-      </c>
-      <c r="U6">
+        <v>2026-06-10T16:24:01.109Z</v>
+      </c>
+      <c r="U6" t="str">
         <v>3181</v>
       </c>
       <c r="V6" t="str">
@@ -894,7 +894,7 @@
       <c r="Z6" t="str">
         <v>SS</v>
       </c>
-      <c r="AA6">
+      <c r="AA6" t="str">
         <v>3</v>
       </c>
     </row>
@@ -924,7 +924,7 @@
         <v>Showroom</v>
       </c>
       <c r="I7" t="str">
-        <v>Section 6</v>
+        <v>Section 2</v>
       </c>
       <c r="J7" t="str">
         <v>C</v>
@@ -933,7 +933,7 @@
         <v>8</v>
       </c>
       <c r="L7" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M7" t="str">
         <v>Available</v>
@@ -954,12 +954,12 @@
         <v/>
       </c>
       <c r="S7" t="str">
-        <v>2026-06-09T18:47:21.255Z</v>
+        <v>2026-06-10T16:24:01.109Z</v>
       </c>
       <c r="T7" t="str">
-        <v>2026-06-09T18:47:21.255Z</v>
-      </c>
-      <c r="U7">
+        <v>2026-06-10T16:24:01.109Z</v>
+      </c>
+      <c r="U7" t="str">
         <v>4089</v>
       </c>
       <c r="V7" t="str">
@@ -977,7 +977,7 @@
       <c r="Z7" t="str">
         <v>SS</v>
       </c>
-      <c r="AA7">
+      <c r="AA7" t="str">
         <v>3</v>
       </c>
     </row>
@@ -1007,7 +1007,7 @@
         <v>Showroom</v>
       </c>
       <c r="I8" t="str">
-        <v>Section 6</v>
+        <v>Section 2</v>
       </c>
       <c r="J8" t="str">
         <v>C</v>
@@ -1016,7 +1016,7 @@
         <v>9</v>
       </c>
       <c r="L8" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M8" t="str">
         <v>Available</v>
@@ -1037,12 +1037,12 @@
         <v/>
       </c>
       <c r="S8" t="str">
-        <v>2026-06-09T18:47:21.255Z</v>
+        <v>2026-06-10T16:24:01.109Z</v>
       </c>
       <c r="T8" t="str">
-        <v>2026-06-09T18:47:21.255Z</v>
-      </c>
-      <c r="U8">
+        <v>2026-06-10T16:24:01.109Z</v>
+      </c>
+      <c r="U8" t="str">
         <v>4551</v>
       </c>
       <c r="V8" t="str">
@@ -1060,7 +1060,7 @@
       <c r="Z8" t="str">
         <v>SS</v>
       </c>
-      <c r="AA8">
+      <c r="AA8" t="str">
         <v>3</v>
       </c>
     </row>
@@ -1090,7 +1090,7 @@
         <v>Showroom</v>
       </c>
       <c r="I9" t="str">
-        <v>Section 6</v>
+        <v>Section 2</v>
       </c>
       <c r="J9" t="str">
         <v>C</v>
@@ -1099,7 +1099,7 @@
         <v>10</v>
       </c>
       <c r="L9" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M9" t="str">
         <v>Available</v>
@@ -1120,12 +1120,12 @@
         <v/>
       </c>
       <c r="S9" t="str">
-        <v>2026-06-09T18:47:21.255Z</v>
+        <v>2026-06-10T16:24:01.109Z</v>
       </c>
       <c r="T9" t="str">
-        <v>2026-06-09T18:47:21.255Z</v>
-      </c>
-      <c r="U9">
+        <v>2026-06-10T16:24:01.109Z</v>
+      </c>
+      <c r="U9" t="str">
         <v>4224</v>
       </c>
       <c r="V9" t="str">
@@ -1143,7 +1143,7 @@
       <c r="Z9" t="str">
         <v>SS</v>
       </c>
-      <c r="AA9">
+      <c r="AA9" t="str">
         <v>5</v>
       </c>
     </row>
@@ -1173,7 +1173,7 @@
         <v>Showroom</v>
       </c>
       <c r="I10" t="str">
-        <v>Section 6</v>
+        <v>Section 2</v>
       </c>
       <c r="J10" t="str">
         <v>C</v>
@@ -1182,7 +1182,7 @@
         <v>11</v>
       </c>
       <c r="L10" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M10" t="str">
         <v>Available</v>
@@ -1203,12 +1203,12 @@
         <v/>
       </c>
       <c r="S10" t="str">
-        <v>2026-06-09T18:47:21.255Z</v>
+        <v>2026-06-10T16:24:01.109Z</v>
       </c>
       <c r="T10" t="str">
-        <v>2026-06-09T18:47:21.255Z</v>
-      </c>
-      <c r="U10">
+        <v>2026-06-10T16:24:01.109Z</v>
+      </c>
+      <c r="U10" t="str">
         <v>4624</v>
       </c>
       <c r="V10" t="str">
@@ -1226,7 +1226,7 @@
       <c r="Z10" t="str">
         <v>SS</v>
       </c>
-      <c r="AA10">
+      <c r="AA10" t="str">
         <v>5</v>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
         <v>Showroom</v>
       </c>
       <c r="I11" t="str">
-        <v>Section 6</v>
+        <v>Section 2</v>
       </c>
       <c r="J11" t="str">
         <v>C</v>
@@ -1265,7 +1265,7 @@
         <v>12</v>
       </c>
       <c r="L11" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M11" t="str">
         <v>Available</v>
@@ -1286,12 +1286,12 @@
         <v/>
       </c>
       <c r="S11" t="str">
-        <v>2026-06-09T18:47:21.255Z</v>
+        <v>2026-06-10T16:24:01.110Z</v>
       </c>
       <c r="T11" t="str">
-        <v>2026-06-09T18:47:21.255Z</v>
-      </c>
-      <c r="U11">
+        <v>2026-06-10T16:24:01.110Z</v>
+      </c>
+      <c r="U11" t="str">
         <v>3116</v>
       </c>
       <c r="V11" t="str">
@@ -1309,7 +1309,7 @@
       <c r="Z11" t="str">
         <v>SS</v>
       </c>
-      <c r="AA11">
+      <c r="AA11" t="str">
         <v>5</v>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         <v>Showroom</v>
       </c>
       <c r="I12" t="str">
-        <v>Section 6</v>
+        <v>Section 2</v>
       </c>
       <c r="J12" t="str">
         <v>C</v>
@@ -1348,7 +1348,7 @@
         <v>17</v>
       </c>
       <c r="L12" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M12" t="str">
         <v>Available</v>
@@ -1369,12 +1369,12 @@
         <v/>
       </c>
       <c r="S12" t="str">
-        <v>2026-06-09T18:47:21.255Z</v>
+        <v>2026-06-10T16:24:01.110Z</v>
       </c>
       <c r="T12" t="str">
-        <v>2026-06-09T18:47:21.255Z</v>
-      </c>
-      <c r="U12">
+        <v>2026-06-10T16:24:01.110Z</v>
+      </c>
+      <c r="U12" t="str">
         <v>5992</v>
       </c>
       <c r="V12" t="str">
@@ -1392,7 +1392,7 @@
       <c r="Z12" t="str">
         <v>SS</v>
       </c>
-      <c r="AA12">
+      <c r="AA12" t="str">
         <v>5</v>
       </c>
     </row>
@@ -1452,10 +1452,10 @@
         <v/>
       </c>
       <c r="S13" t="str">
-        <v>2026-06-09T18:47:21.255Z</v>
+        <v>2026-06-10T16:24:01.110Z</v>
       </c>
       <c r="T13" t="str">
-        <v>2026-06-10T15:58:49.455Z</v>
+        <v>2026-06-10T16:24:01.110Z</v>
       </c>
       <c r="U13" t="str">
         <v>6525</v>
@@ -1505,7 +1505,7 @@
         <v>Showroom</v>
       </c>
       <c r="I14" t="str">
-        <v>Section 6</v>
+        <v>Section 2</v>
       </c>
       <c r="J14" t="str">
         <v>D</v>
@@ -1514,7 +1514,7 @@
         <v>5</v>
       </c>
       <c r="L14" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M14" t="str">
         <v>Available</v>
@@ -1535,12 +1535,12 @@
         <v/>
       </c>
       <c r="S14" t="str">
-        <v>2026-06-09T18:47:21.255Z</v>
+        <v>2026-06-10T16:24:01.110Z</v>
       </c>
       <c r="T14" t="str">
-        <v>2026-06-09T18:47:21.255Z</v>
-      </c>
-      <c r="U14">
+        <v>2026-06-10T16:24:01.110Z</v>
+      </c>
+      <c r="U14" t="str">
         <v>5522</v>
       </c>
       <c r="V14" t="str">
@@ -1558,7 +1558,7 @@
       <c r="Z14" t="str">
         <v>SS</v>
       </c>
-      <c r="AA14">
+      <c r="AA14" t="str">
         <v>5</v>
       </c>
     </row>
@@ -1588,7 +1588,7 @@
         <v>Showroom</v>
       </c>
       <c r="I15" t="str">
-        <v>Section 6</v>
+        <v>Section 2</v>
       </c>
       <c r="J15" t="str">
         <v>D</v>
@@ -1597,7 +1597,7 @@
         <v>6</v>
       </c>
       <c r="L15" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M15" t="str">
         <v>Available</v>
@@ -1618,12 +1618,12 @@
         <v/>
       </c>
       <c r="S15" t="str">
-        <v>2026-06-09T18:47:21.256Z</v>
+        <v>2026-06-10T16:24:01.110Z</v>
       </c>
       <c r="T15" t="str">
-        <v>2026-06-09T18:47:21.256Z</v>
-      </c>
-      <c r="U15">
+        <v>2026-06-10T16:24:01.110Z</v>
+      </c>
+      <c r="U15" t="str">
         <v>9926</v>
       </c>
       <c r="V15" t="str">
@@ -1641,7 +1641,7 @@
       <c r="Z15" t="str">
         <v>SS</v>
       </c>
-      <c r="AA15">
+      <c r="AA15" t="str">
         <v>5</v>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
         <v>Showroom</v>
       </c>
       <c r="I16" t="str">
-        <v>Section 6</v>
+        <v>Section 2</v>
       </c>
       <c r="J16" t="str">
         <v>D</v>
@@ -1680,7 +1680,7 @@
         <v>9</v>
       </c>
       <c r="L16" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M16" t="str">
         <v>Available</v>
@@ -1701,12 +1701,12 @@
         <v/>
       </c>
       <c r="S16" t="str">
-        <v>2026-06-09T18:47:21.256Z</v>
+        <v>2026-06-10T16:24:01.112Z</v>
       </c>
       <c r="T16" t="str">
-        <v>2026-06-09T18:47:21.256Z</v>
-      </c>
-      <c r="U16">
+        <v>2026-06-10T16:24:01.112Z</v>
+      </c>
+      <c r="U16" t="str">
         <v>9925</v>
       </c>
       <c r="V16" t="str">
@@ -1724,7 +1724,7 @@
       <c r="Z16" t="str">
         <v>SS</v>
       </c>
-      <c r="AA16">
+      <c r="AA16" t="str">
         <v>12</v>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
         <v>Showroom</v>
       </c>
       <c r="I17" t="str">
-        <v>Section 6</v>
+        <v>Section 2</v>
       </c>
       <c r="J17" t="str">
         <v>D</v>
@@ -1763,7 +1763,7 @@
         <v>11</v>
       </c>
       <c r="L17" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M17" t="str">
         <v>Available</v>
@@ -1784,12 +1784,12 @@
         <v/>
       </c>
       <c r="S17" t="str">
-        <v>2026-06-09T18:47:21.256Z</v>
+        <v>2026-06-10T16:24:01.112Z</v>
       </c>
       <c r="T17" t="str">
-        <v>2026-06-09T18:47:21.256Z</v>
-      </c>
-      <c r="U17">
+        <v>2026-06-10T16:24:01.112Z</v>
+      </c>
+      <c r="U17" t="str">
         <v>2005</v>
       </c>
       <c r="V17" t="str">
@@ -1807,7 +1807,7 @@
       <c r="Z17" t="str">
         <v>SS</v>
       </c>
-      <c r="AA17">
+      <c r="AA17" t="str">
         <v>12</v>
       </c>
     </row>
@@ -1837,7 +1837,7 @@
         <v>Showroom</v>
       </c>
       <c r="I18" t="str">
-        <v>Section 6</v>
+        <v>Section 2</v>
       </c>
       <c r="J18" t="str">
         <v>D</v>
@@ -1846,7 +1846,7 @@
         <v>12</v>
       </c>
       <c r="L18" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M18" t="str">
         <v>Available</v>
@@ -1867,12 +1867,12 @@
         <v/>
       </c>
       <c r="S18" t="str">
-        <v>2026-06-09T18:47:21.256Z</v>
+        <v>2026-06-10T16:24:01.112Z</v>
       </c>
       <c r="T18" t="str">
-        <v>2026-06-09T18:47:21.256Z</v>
-      </c>
-      <c r="U18">
+        <v>2026-06-10T16:24:01.112Z</v>
+      </c>
+      <c r="U18" t="str">
         <v>10178</v>
       </c>
       <c r="V18" t="str">
@@ -1890,7 +1890,7 @@
       <c r="Z18" t="str">
         <v>SS</v>
       </c>
-      <c r="AA18">
+      <c r="AA18" t="str">
         <v>12</v>
       </c>
     </row>
@@ -1920,7 +1920,7 @@
         <v>Showroom</v>
       </c>
       <c r="I19" t="str">
-        <v>Section 7</v>
+        <v>Section 3</v>
       </c>
       <c r="J19" t="str">
         <v>E</v>
@@ -1929,7 +1929,7 @@
         <v>4</v>
       </c>
       <c r="L19" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M19" t="str">
         <v>Available</v>
@@ -1950,12 +1950,12 @@
         <v/>
       </c>
       <c r="S19" t="str">
-        <v>2026-06-09T18:47:21.256Z</v>
+        <v>2026-06-10T16:24:01.112Z</v>
       </c>
       <c r="T19" t="str">
-        <v>2026-06-09T18:47:21.256Z</v>
-      </c>
-      <c r="U19">
+        <v>2026-06-10T16:24:01.112Z</v>
+      </c>
+      <c r="U19" t="str">
         <v>9660</v>
       </c>
       <c r="V19" t="str">
@@ -1973,7 +1973,7 @@
       <c r="Z19" t="str">
         <v>SS</v>
       </c>
-      <c r="AA19">
+      <c r="AA19" t="str">
         <v>12</v>
       </c>
     </row>
@@ -2003,7 +2003,7 @@
         <v>Showroom</v>
       </c>
       <c r="I20" t="str">
-        <v>Section 7</v>
+        <v>Section 3</v>
       </c>
       <c r="J20" t="str">
         <v>E</v>
@@ -2012,7 +2012,7 @@
         <v>5</v>
       </c>
       <c r="L20" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M20" t="str">
         <v>Available</v>
@@ -2033,12 +2033,12 @@
         <v/>
       </c>
       <c r="S20" t="str">
-        <v>2026-06-09T18:47:21.256Z</v>
+        <v>2026-06-10T16:24:01.113Z</v>
       </c>
       <c r="T20" t="str">
-        <v>2026-06-09T18:47:21.256Z</v>
-      </c>
-      <c r="U20">
+        <v>2026-06-10T16:24:01.113Z</v>
+      </c>
+      <c r="U20" t="str">
         <v>9112</v>
       </c>
       <c r="V20" t="str">
@@ -2056,7 +2056,7 @@
       <c r="Z20" t="str">
         <v>SS</v>
       </c>
-      <c r="AA20">
+      <c r="AA20" t="str">
         <v>36</v>
       </c>
     </row>
@@ -2086,7 +2086,7 @@
         <v>Showroom</v>
       </c>
       <c r="I21" t="str">
-        <v>Section 7</v>
+        <v>Section 3</v>
       </c>
       <c r="J21" t="str">
         <v>E</v>
@@ -2095,7 +2095,7 @@
         <v>8</v>
       </c>
       <c r="L21" t="str">
-        <v>Indoor Display</v>
+        <v/>
       </c>
       <c r="M21" t="str">
         <v>Available</v>
@@ -2116,12 +2116,12 @@
         <v/>
       </c>
       <c r="S21" t="str">
-        <v>2026-06-09T18:47:21.256Z</v>
+        <v>2026-06-10T16:24:01.113Z</v>
       </c>
       <c r="T21" t="str">
-        <v>2026-06-09T18:47:21.256Z</v>
-      </c>
-      <c r="U21">
+        <v>2026-06-10T16:24:01.113Z</v>
+      </c>
+      <c r="U21" t="str">
         <v>8379</v>
       </c>
       <c r="V21" t="str">
@@ -2139,7 +2139,7 @@
       <c r="Z21" t="str">
         <v>SS</v>
       </c>
-      <c r="AA21">
+      <c r="AA21" t="str">
         <v>36</v>
       </c>
     </row>
@@ -2199,10 +2199,10 @@
         <v/>
       </c>
       <c r="S22" t="str">
-        <v>2026-06-10T15:43:18.235Z</v>
+        <v>2026-06-10T16:24:01.113Z</v>
       </c>
       <c r="T22" t="str">
-        <v>2026-06-10T15:57:52.007Z</v>
+        <v>2026-06-10T16:24:01.113Z</v>
       </c>
       <c r="U22" t="str">
         <v>5555</v>

--- a/data/yard-inventory.xlsx
+++ b/data/yard-inventory.xlsx
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="M13" t="str">
-        <v>Rental Ready</v>
+        <v>Available</v>
       </c>
       <c r="N13" t="str">
         <v>Ready</v>
@@ -1455,7 +1455,7 @@
         <v>2026-06-10T16:24:01.110Z</v>
       </c>
       <c r="T13" t="str">
-        <v>2026-06-10T16:24:01.110Z</v>
+        <v>2026-06-10T18:06:10.510Z</v>
       </c>
       <c r="U13" t="str">
         <v>6525</v>
@@ -2166,16 +2166,16 @@
         <v>2000</v>
       </c>
       <c r="H22" t="str">
-        <v>Transportation Bay</v>
+        <v>Yard</v>
       </c>
       <c r="I22" t="str">
-        <v>Inbound</v>
+        <v>Section 1</v>
       </c>
       <c r="J22" t="str">
-        <v>C</v>
+        <v>A</v>
       </c>
       <c r="K22" t="str">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L22" t="str">
         <v/>
@@ -2190,7 +2190,7 @@
         <v>No</v>
       </c>
       <c r="P22" t="str">
-        <v>2026-06-10</v>
+        <v>2026-06-11</v>
       </c>
       <c r="Q22" t="str">
         <v/>
@@ -2202,7 +2202,7 @@
         <v>2026-06-10T16:24:01.113Z</v>
       </c>
       <c r="T22" t="str">
-        <v>2026-06-10T16:24:01.113Z</v>
+        <v>2026-06-11T00:03:29.694Z</v>
       </c>
       <c r="U22" t="str">
         <v>5555</v>

--- a/data/yard-inventory.xlsx
+++ b/data/yard-inventory.xlsx
@@ -2166,7 +2166,7 @@
         <v>2000</v>
       </c>
       <c r="H22" t="str">
-        <v>Yard</v>
+        <v>Showroom</v>
       </c>
       <c r="I22" t="str">
         <v>Section 1</v>
@@ -2175,7 +2175,7 @@
         <v>A</v>
       </c>
       <c r="K22" t="str">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="L22" t="str">
         <v/>
@@ -2190,7 +2190,7 @@
         <v>No</v>
       </c>
       <c r="P22" t="str">
-        <v>2026-06-11</v>
+        <v>2026-06-16</v>
       </c>
       <c r="Q22" t="str">
         <v/>
@@ -2202,7 +2202,7 @@
         <v>2026-06-10T16:24:01.113Z</v>
       </c>
       <c r="T22" t="str">
-        <v>2026-06-11T00:03:29.694Z</v>
+        <v>2026-06-16T14:20:58.758Z</v>
       </c>
       <c r="U22" t="str">
         <v>5555</v>
